--- a/artfynd/A 34540-2025 artfynd.xlsx
+++ b/artfynd/A 34540-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1436,6 +1436,782 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>128518179</v>
+      </c>
+      <c r="B8" t="n">
+        <v>92754</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>4366</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Strandåker, Jmt</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>555066</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6961789</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>128518177</v>
+      </c>
+      <c r="B9" t="n">
+        <v>92754</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>4366</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Strandåker, Jmt</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>555040</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6961886</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>128518172</v>
+      </c>
+      <c r="B10" t="n">
+        <v>90954</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>256703</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tallfingersvamp</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Ramaria eosanguinea</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>R.H.Petersen</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Strandåker, Jmt</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>555056</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6961814</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>128518184</v>
+      </c>
+      <c r="B11" t="n">
+        <v>98571</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Strandåker, Jmt</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>555042</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6961890</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>128518175</v>
+      </c>
+      <c r="B12" t="n">
+        <v>92754</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>4366</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Strandåker, Jmt</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>554991</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6961943</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>128518169</v>
+      </c>
+      <c r="B13" t="n">
+        <v>57845</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Strandåker, Jmt</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>554998</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6962106</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>128518178</v>
+      </c>
+      <c r="B14" t="n">
+        <v>92754</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>4366</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Strandåker, Jmt</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>555051</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6961818</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>128518176</v>
+      </c>
+      <c r="B15" t="n">
+        <v>92754</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>4366</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Strandåker, Jmt</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>555032</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6961940</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 34540-2025 artfynd.xlsx
+++ b/artfynd/A 34540-2025 artfynd.xlsx
@@ -1633,10 +1633,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128518172</v>
+        <v>128518175</v>
       </c>
       <c r="B10" t="n">
-        <v>90954</v>
+        <v>92754</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1644,21 +1644,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>256703</v>
+        <v>4366</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1668,10 +1668,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>555056</v>
+        <v>554991</v>
       </c>
       <c r="R10" t="n">
-        <v>6961814</v>
+        <v>6961943</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1827,10 +1827,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128518175</v>
+        <v>128518172</v>
       </c>
       <c r="B12" t="n">
-        <v>92754</v>
+        <v>90954</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1838,21 +1838,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4366</v>
+        <v>256703</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Tallfingersvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Ramaria eosanguinea</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>R.H.Petersen</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1862,10 +1862,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>554991</v>
+        <v>555056</v>
       </c>
       <c r="R12" t="n">
-        <v>6961943</v>
+        <v>6961814</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>

--- a/artfynd/A 34540-2025 artfynd.xlsx
+++ b/artfynd/A 34540-2025 artfynd.xlsx
@@ -1442,7 +1442,7 @@
         <v>128518179</v>
       </c>
       <c r="B8" t="n">
-        <v>92754</v>
+        <v>92760</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1539,7 +1539,7 @@
         <v>128518177</v>
       </c>
       <c r="B9" t="n">
-        <v>92754</v>
+        <v>92760</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1633,32 +1633,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128518175</v>
+        <v>128518184</v>
       </c>
       <c r="B10" t="n">
-        <v>92754</v>
+        <v>98579</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4366</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1668,10 +1668,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>554991</v>
+        <v>555042</v>
       </c>
       <c r="R10" t="n">
-        <v>6961943</v>
+        <v>6961890</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1730,32 +1730,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128518184</v>
+        <v>128518172</v>
       </c>
       <c r="B11" t="n">
-        <v>98571</v>
+        <v>90960</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>256703</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallfingersvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ramaria eosanguinea</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>R.H.Petersen</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1765,10 +1765,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>555042</v>
+        <v>555056</v>
       </c>
       <c r="R11" t="n">
-        <v>6961890</v>
+        <v>6961814</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1827,10 +1827,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128518172</v>
+        <v>128518175</v>
       </c>
       <c r="B12" t="n">
-        <v>90954</v>
+        <v>92760</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1838,21 +1838,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>256703</v>
+        <v>4366</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1862,10 +1862,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>555056</v>
+        <v>554991</v>
       </c>
       <c r="R12" t="n">
-        <v>6961814</v>
+        <v>6961943</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1927,7 +1927,7 @@
         <v>128518169</v>
       </c>
       <c r="B13" t="n">
-        <v>57845</v>
+        <v>57849</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2024,7 +2024,7 @@
         <v>128518178</v>
       </c>
       <c r="B14" t="n">
-        <v>92754</v>
+        <v>92760</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2121,7 +2121,7 @@
         <v>128518176</v>
       </c>
       <c r="B15" t="n">
-        <v>92754</v>
+        <v>92760</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 34540-2025 artfynd.xlsx
+++ b/artfynd/A 34540-2025 artfynd.xlsx
@@ -1442,7 +1442,7 @@
         <v>128518179</v>
       </c>
       <c r="B8" t="n">
-        <v>92760</v>
+        <v>92766</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1539,7 +1539,7 @@
         <v>128518177</v>
       </c>
       <c r="B9" t="n">
-        <v>92760</v>
+        <v>92766</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1636,7 +1636,7 @@
         <v>128518184</v>
       </c>
       <c r="B10" t="n">
-        <v>98579</v>
+        <v>98585</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1733,7 +1733,7 @@
         <v>128518172</v>
       </c>
       <c r="B11" t="n">
-        <v>90960</v>
+        <v>90966</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1830,7 +1830,7 @@
         <v>128518175</v>
       </c>
       <c r="B12" t="n">
-        <v>92760</v>
+        <v>92766</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2024,7 +2024,7 @@
         <v>128518178</v>
       </c>
       <c r="B14" t="n">
-        <v>92760</v>
+        <v>92766</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2121,7 +2121,7 @@
         <v>128518176</v>
       </c>
       <c r="B15" t="n">
-        <v>92760</v>
+        <v>92766</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 34540-2025 artfynd.xlsx
+++ b/artfynd/A 34540-2025 artfynd.xlsx
@@ -1633,32 +1633,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128518184</v>
+        <v>128518172</v>
       </c>
       <c r="B10" t="n">
-        <v>98585</v>
+        <v>90966</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>256703</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallfingersvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ramaria eosanguinea</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>R.H.Petersen</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1668,10 +1668,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>555042</v>
+        <v>555056</v>
       </c>
       <c r="R10" t="n">
-        <v>6961890</v>
+        <v>6961814</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1730,10 +1730,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128518172</v>
+        <v>128518175</v>
       </c>
       <c r="B11" t="n">
-        <v>90966</v>
+        <v>92766</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1741,21 +1741,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>256703</v>
+        <v>4366</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1765,10 +1765,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>555056</v>
+        <v>554991</v>
       </c>
       <c r="R11" t="n">
-        <v>6961814</v>
+        <v>6961943</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1827,32 +1827,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128518175</v>
+        <v>128518184</v>
       </c>
       <c r="B12" t="n">
-        <v>92766</v>
+        <v>98585</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4366</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1862,10 +1862,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>554991</v>
+        <v>555042</v>
       </c>
       <c r="R12" t="n">
-        <v>6961943</v>
+        <v>6961890</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>

--- a/artfynd/A 34540-2025 artfynd.xlsx
+++ b/artfynd/A 34540-2025 artfynd.xlsx
@@ -1442,7 +1442,7 @@
         <v>128518179</v>
       </c>
       <c r="B8" t="n">
-        <v>92766</v>
+        <v>92768</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1539,7 +1539,7 @@
         <v>128518177</v>
       </c>
       <c r="B9" t="n">
-        <v>92766</v>
+        <v>92768</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1633,10 +1633,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128518172</v>
+        <v>128518175</v>
       </c>
       <c r="B10" t="n">
-        <v>90966</v>
+        <v>92768</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1644,21 +1644,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>256703</v>
+        <v>4366</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1668,10 +1668,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>555056</v>
+        <v>554991</v>
       </c>
       <c r="R10" t="n">
-        <v>6961814</v>
+        <v>6961943</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1730,32 +1730,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128518175</v>
+        <v>128518184</v>
       </c>
       <c r="B11" t="n">
-        <v>92766</v>
+        <v>98588</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4366</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1765,10 +1765,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>554991</v>
+        <v>555042</v>
       </c>
       <c r="R11" t="n">
-        <v>6961943</v>
+        <v>6961890</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1827,32 +1827,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128518184</v>
+        <v>128518172</v>
       </c>
       <c r="B12" t="n">
-        <v>98585</v>
+        <v>90968</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>256703</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallfingersvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ramaria eosanguinea</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>R.H.Petersen</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1862,10 +1862,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>555042</v>
+        <v>555056</v>
       </c>
       <c r="R12" t="n">
-        <v>6961890</v>
+        <v>6961814</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2024,7 +2024,7 @@
         <v>128518178</v>
       </c>
       <c r="B14" t="n">
-        <v>92766</v>
+        <v>92768</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2121,7 +2121,7 @@
         <v>128518176</v>
       </c>
       <c r="B15" t="n">
-        <v>92766</v>
+        <v>92768</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 34540-2025 artfynd.xlsx
+++ b/artfynd/A 34540-2025 artfynd.xlsx
@@ -1730,32 +1730,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128518184</v>
+        <v>128518172</v>
       </c>
       <c r="B11" t="n">
-        <v>98588</v>
+        <v>90968</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>256703</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallfingersvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ramaria eosanguinea</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>R.H.Petersen</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1765,10 +1765,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>555042</v>
+        <v>555056</v>
       </c>
       <c r="R11" t="n">
-        <v>6961890</v>
+        <v>6961814</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1827,32 +1827,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128518172</v>
+        <v>128518184</v>
       </c>
       <c r="B12" t="n">
-        <v>90968</v>
+        <v>98591</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>256703</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1862,10 +1862,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>555056</v>
+        <v>555042</v>
       </c>
       <c r="R12" t="n">
-        <v>6961814</v>
+        <v>6961890</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>

--- a/artfynd/A 34540-2025 artfynd.xlsx
+++ b/artfynd/A 34540-2025 artfynd.xlsx
@@ -1442,7 +1442,7 @@
         <v>128518179</v>
       </c>
       <c r="B8" t="n">
-        <v>92768</v>
+        <v>92769</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1539,7 +1539,7 @@
         <v>128518177</v>
       </c>
       <c r="B9" t="n">
-        <v>92768</v>
+        <v>92769</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1636,7 +1636,7 @@
         <v>128518175</v>
       </c>
       <c r="B10" t="n">
-        <v>92768</v>
+        <v>92769</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1730,32 +1730,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128518172</v>
+        <v>128518184</v>
       </c>
       <c r="B11" t="n">
-        <v>90968</v>
+        <v>98592</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>256703</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1765,10 +1765,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>555056</v>
+        <v>555042</v>
       </c>
       <c r="R11" t="n">
-        <v>6961814</v>
+        <v>6961890</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1827,32 +1827,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128518184</v>
+        <v>128518172</v>
       </c>
       <c r="B12" t="n">
-        <v>98591</v>
+        <v>90969</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>256703</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallfingersvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ramaria eosanguinea</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>R.H.Petersen</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1862,10 +1862,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>555042</v>
+        <v>555056</v>
       </c>
       <c r="R12" t="n">
-        <v>6961890</v>
+        <v>6961814</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2024,7 +2024,7 @@
         <v>128518178</v>
       </c>
       <c r="B14" t="n">
-        <v>92768</v>
+        <v>92769</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2121,7 +2121,7 @@
         <v>128518176</v>
       </c>
       <c r="B15" t="n">
-        <v>92768</v>
+        <v>92769</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 34540-2025 artfynd.xlsx
+++ b/artfynd/A 34540-2025 artfynd.xlsx
@@ -1442,7 +1442,7 @@
         <v>128518179</v>
       </c>
       <c r="B8" t="n">
-        <v>92769</v>
+        <v>92796</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1539,7 +1539,7 @@
         <v>128518177</v>
       </c>
       <c r="B9" t="n">
-        <v>92769</v>
+        <v>92796</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1633,32 +1633,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128518175</v>
+        <v>128518184</v>
       </c>
       <c r="B10" t="n">
-        <v>92769</v>
+        <v>98619</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4366</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1668,10 +1668,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>554991</v>
+        <v>555042</v>
       </c>
       <c r="R10" t="n">
-        <v>6961943</v>
+        <v>6961890</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1730,32 +1730,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128518184</v>
+        <v>128518172</v>
       </c>
       <c r="B11" t="n">
-        <v>98592</v>
+        <v>90996</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>256703</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallfingersvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ramaria eosanguinea</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>R.H.Petersen</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1765,10 +1765,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>555042</v>
+        <v>555056</v>
       </c>
       <c r="R11" t="n">
-        <v>6961890</v>
+        <v>6961814</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1827,10 +1827,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128518172</v>
+        <v>128518175</v>
       </c>
       <c r="B12" t="n">
-        <v>90969</v>
+        <v>92796</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1838,21 +1838,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>256703</v>
+        <v>4366</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1862,10 +1862,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>555056</v>
+        <v>554991</v>
       </c>
       <c r="R12" t="n">
-        <v>6961814</v>
+        <v>6961943</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1927,7 +1927,7 @@
         <v>128518169</v>
       </c>
       <c r="B13" t="n">
-        <v>57849</v>
+        <v>57876</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2024,7 +2024,7 @@
         <v>128518178</v>
       </c>
       <c r="B14" t="n">
-        <v>92769</v>
+        <v>92796</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2121,7 +2121,7 @@
         <v>128518176</v>
       </c>
       <c r="B15" t="n">
-        <v>92769</v>
+        <v>92796</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 34540-2025 artfynd.xlsx
+++ b/artfynd/A 34540-2025 artfynd.xlsx
@@ -1633,32 +1633,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128518184</v>
+        <v>128518175</v>
       </c>
       <c r="B10" t="n">
-        <v>98619</v>
+        <v>92796</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>4366</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1668,10 +1668,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>555042</v>
+        <v>554991</v>
       </c>
       <c r="R10" t="n">
-        <v>6961890</v>
+        <v>6961943</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1730,32 +1730,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128518172</v>
+        <v>128518184</v>
       </c>
       <c r="B11" t="n">
-        <v>90996</v>
+        <v>98619</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>256703</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1765,10 +1765,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>555056</v>
+        <v>555042</v>
       </c>
       <c r="R11" t="n">
-        <v>6961814</v>
+        <v>6961890</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1827,10 +1827,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128518175</v>
+        <v>128518172</v>
       </c>
       <c r="B12" t="n">
-        <v>92796</v>
+        <v>90996</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1838,21 +1838,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4366</v>
+        <v>256703</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Tallfingersvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Ramaria eosanguinea</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>R.H.Petersen</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1862,10 +1862,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>554991</v>
+        <v>555056</v>
       </c>
       <c r="R12" t="n">
-        <v>6961943</v>
+        <v>6961814</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>

--- a/artfynd/A 34540-2025 artfynd.xlsx
+++ b/artfynd/A 34540-2025 artfynd.xlsx
@@ -1442,7 +1442,7 @@
         <v>128518179</v>
       </c>
       <c r="B8" t="n">
-        <v>92796</v>
+        <v>92801</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1539,7 +1539,7 @@
         <v>128518177</v>
       </c>
       <c r="B9" t="n">
-        <v>92796</v>
+        <v>92801</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1633,32 +1633,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128518175</v>
+        <v>128518184</v>
       </c>
       <c r="B10" t="n">
-        <v>92796</v>
+        <v>98625</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4366</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1668,10 +1668,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>554991</v>
+        <v>555042</v>
       </c>
       <c r="R10" t="n">
-        <v>6961943</v>
+        <v>6961890</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1730,32 +1730,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128518184</v>
+        <v>128518172</v>
       </c>
       <c r="B11" t="n">
-        <v>98619</v>
+        <v>91001</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>256703</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallfingersvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ramaria eosanguinea</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>R.H.Petersen</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1765,10 +1765,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>555042</v>
+        <v>555056</v>
       </c>
       <c r="R11" t="n">
-        <v>6961890</v>
+        <v>6961814</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1827,10 +1827,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128518172</v>
+        <v>128518175</v>
       </c>
       <c r="B12" t="n">
-        <v>90996</v>
+        <v>92801</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1838,21 +1838,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>256703</v>
+        <v>4366</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1862,10 +1862,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>555056</v>
+        <v>554991</v>
       </c>
       <c r="R12" t="n">
-        <v>6961814</v>
+        <v>6961943</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2024,7 +2024,7 @@
         <v>128518178</v>
       </c>
       <c r="B14" t="n">
-        <v>92796</v>
+        <v>92801</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2121,7 +2121,7 @@
         <v>128518176</v>
       </c>
       <c r="B15" t="n">
-        <v>92796</v>
+        <v>92801</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 34540-2025 artfynd.xlsx
+++ b/artfynd/A 34540-2025 artfynd.xlsx
@@ -1442,7 +1442,7 @@
         <v>128518179</v>
       </c>
       <c r="B8" t="n">
-        <v>92801</v>
+        <v>92806</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1539,7 +1539,7 @@
         <v>128518177</v>
       </c>
       <c r="B9" t="n">
-        <v>92801</v>
+        <v>92806</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1633,32 +1633,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128518184</v>
+        <v>128518175</v>
       </c>
       <c r="B10" t="n">
-        <v>98625</v>
+        <v>92806</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>4366</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1668,10 +1668,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>555042</v>
+        <v>554991</v>
       </c>
       <c r="R10" t="n">
-        <v>6961890</v>
+        <v>6961943</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1730,32 +1730,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128518172</v>
+        <v>128518184</v>
       </c>
       <c r="B11" t="n">
-        <v>91001</v>
+        <v>98632</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>256703</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1765,10 +1765,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>555056</v>
+        <v>555042</v>
       </c>
       <c r="R11" t="n">
-        <v>6961814</v>
+        <v>6961890</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1827,10 +1827,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128518175</v>
+        <v>128518172</v>
       </c>
       <c r="B12" t="n">
-        <v>92801</v>
+        <v>91006</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1838,21 +1838,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4366</v>
+        <v>256703</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Tallfingersvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Ramaria eosanguinea</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>R.H.Petersen</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1862,10 +1862,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>554991</v>
+        <v>555056</v>
       </c>
       <c r="R12" t="n">
-        <v>6961943</v>
+        <v>6961814</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2024,7 +2024,7 @@
         <v>128518178</v>
       </c>
       <c r="B14" t="n">
-        <v>92801</v>
+        <v>92806</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2121,7 +2121,7 @@
         <v>128518176</v>
       </c>
       <c r="B15" t="n">
-        <v>92801</v>
+        <v>92806</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 34540-2025 artfynd.xlsx
+++ b/artfynd/A 34540-2025 artfynd.xlsx
@@ -1633,32 +1633,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128518175</v>
+        <v>128518184</v>
       </c>
       <c r="B10" t="n">
-        <v>92806</v>
+        <v>98632</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4366</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1668,10 +1668,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>554991</v>
+        <v>555042</v>
       </c>
       <c r="R10" t="n">
-        <v>6961943</v>
+        <v>6961890</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1730,32 +1730,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128518184</v>
+        <v>128518172</v>
       </c>
       <c r="B11" t="n">
-        <v>98632</v>
+        <v>91006</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>256703</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallfingersvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ramaria eosanguinea</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>R.H.Petersen</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1765,10 +1765,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>555042</v>
+        <v>555056</v>
       </c>
       <c r="R11" t="n">
-        <v>6961890</v>
+        <v>6961814</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1827,10 +1827,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128518172</v>
+        <v>128518175</v>
       </c>
       <c r="B12" t="n">
-        <v>91006</v>
+        <v>92806</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1838,21 +1838,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>256703</v>
+        <v>4366</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1862,10 +1862,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>555056</v>
+        <v>554991</v>
       </c>
       <c r="R12" t="n">
-        <v>6961814</v>
+        <v>6961943</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>

--- a/artfynd/A 34540-2025 artfynd.xlsx
+++ b/artfynd/A 34540-2025 artfynd.xlsx
@@ -1442,7 +1442,7 @@
         <v>128518179</v>
       </c>
       <c r="B8" t="n">
-        <v>92806</v>
+        <v>92810</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1539,7 +1539,7 @@
         <v>128518177</v>
       </c>
       <c r="B9" t="n">
-        <v>92806</v>
+        <v>92810</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1633,32 +1633,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128518184</v>
+        <v>128518172</v>
       </c>
       <c r="B10" t="n">
-        <v>98632</v>
+        <v>91010</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>256703</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallfingersvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ramaria eosanguinea</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>R.H.Petersen</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1668,10 +1668,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>555042</v>
+        <v>555056</v>
       </c>
       <c r="R10" t="n">
-        <v>6961890</v>
+        <v>6961814</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1730,10 +1730,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128518172</v>
+        <v>128518175</v>
       </c>
       <c r="B11" t="n">
-        <v>91006</v>
+        <v>92810</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1741,21 +1741,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>256703</v>
+        <v>4366</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1765,10 +1765,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>555056</v>
+        <v>554991</v>
       </c>
       <c r="R11" t="n">
-        <v>6961814</v>
+        <v>6961943</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1827,32 +1827,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128518175</v>
+        <v>128518184</v>
       </c>
       <c r="B12" t="n">
-        <v>92806</v>
+        <v>98636</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4366</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1862,10 +1862,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>554991</v>
+        <v>555042</v>
       </c>
       <c r="R12" t="n">
-        <v>6961943</v>
+        <v>6961890</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1927,7 +1927,7 @@
         <v>128518169</v>
       </c>
       <c r="B13" t="n">
-        <v>57876</v>
+        <v>57880</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2024,7 +2024,7 @@
         <v>128518178</v>
       </c>
       <c r="B14" t="n">
-        <v>92806</v>
+        <v>92810</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2121,7 +2121,7 @@
         <v>128518176</v>
       </c>
       <c r="B15" t="n">
-        <v>92806</v>
+        <v>92810</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 34540-2025 artfynd.xlsx
+++ b/artfynd/A 34540-2025 artfynd.xlsx
@@ -1633,32 +1633,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128518172</v>
+        <v>128518184</v>
       </c>
       <c r="B10" t="n">
-        <v>91010</v>
+        <v>98636</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>256703</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1668,10 +1668,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>555056</v>
+        <v>555042</v>
       </c>
       <c r="R10" t="n">
-        <v>6961814</v>
+        <v>6961890</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1827,32 +1827,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128518184</v>
+        <v>128518172</v>
       </c>
       <c r="B12" t="n">
-        <v>98636</v>
+        <v>91010</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>256703</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallfingersvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ramaria eosanguinea</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>R.H.Petersen</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1862,10 +1862,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>555042</v>
+        <v>555056</v>
       </c>
       <c r="R12" t="n">
-        <v>6961890</v>
+        <v>6961814</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>

--- a/artfynd/A 34540-2025 artfynd.xlsx
+++ b/artfynd/A 34540-2025 artfynd.xlsx
@@ -1730,10 +1730,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128518175</v>
+        <v>128518172</v>
       </c>
       <c r="B11" t="n">
-        <v>92810</v>
+        <v>91010</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1741,21 +1741,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4366</v>
+        <v>256703</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Tallfingersvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Ramaria eosanguinea</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>R.H.Petersen</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1765,10 +1765,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>554991</v>
+        <v>555056</v>
       </c>
       <c r="R11" t="n">
-        <v>6961943</v>
+        <v>6961814</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1827,10 +1827,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128518172</v>
+        <v>128518175</v>
       </c>
       <c r="B12" t="n">
-        <v>91010</v>
+        <v>92810</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1838,21 +1838,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>256703</v>
+        <v>4366</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1862,10 +1862,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>555056</v>
+        <v>554991</v>
       </c>
       <c r="R12" t="n">
-        <v>6961814</v>
+        <v>6961943</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>

--- a/artfynd/A 34540-2025 artfynd.xlsx
+++ b/artfynd/A 34540-2025 artfynd.xlsx
@@ -1442,7 +1442,7 @@
         <v>128518179</v>
       </c>
       <c r="B8" t="n">
-        <v>92810</v>
+        <v>92815</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1539,7 +1539,7 @@
         <v>128518177</v>
       </c>
       <c r="B9" t="n">
-        <v>92810</v>
+        <v>92815</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1633,32 +1633,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128518184</v>
+        <v>128518172</v>
       </c>
       <c r="B10" t="n">
-        <v>98636</v>
+        <v>91015</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>256703</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallfingersvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ramaria eosanguinea</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>R.H.Petersen</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1668,10 +1668,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>555042</v>
+        <v>555056</v>
       </c>
       <c r="R10" t="n">
-        <v>6961890</v>
+        <v>6961814</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1730,10 +1730,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128518172</v>
+        <v>128518175</v>
       </c>
       <c r="B11" t="n">
-        <v>91010</v>
+        <v>92815</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1741,21 +1741,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>256703</v>
+        <v>4366</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1765,10 +1765,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>555056</v>
+        <v>554991</v>
       </c>
       <c r="R11" t="n">
-        <v>6961814</v>
+        <v>6961943</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1827,32 +1827,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128518175</v>
+        <v>128518184</v>
       </c>
       <c r="B12" t="n">
-        <v>92810</v>
+        <v>98643</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4366</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1862,10 +1862,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>554991</v>
+        <v>555042</v>
       </c>
       <c r="R12" t="n">
-        <v>6961943</v>
+        <v>6961890</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1927,7 +1927,7 @@
         <v>128518169</v>
       </c>
       <c r="B13" t="n">
-        <v>57880</v>
+        <v>57883</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2024,7 +2024,7 @@
         <v>128518178</v>
       </c>
       <c r="B14" t="n">
-        <v>92810</v>
+        <v>92815</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2121,7 +2121,7 @@
         <v>128518176</v>
       </c>
       <c r="B15" t="n">
-        <v>92810</v>
+        <v>92815</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 34540-2025 artfynd.xlsx
+++ b/artfynd/A 34540-2025 artfynd.xlsx
@@ -1442,7 +1442,7 @@
         <v>128518179</v>
       </c>
       <c r="B8" t="n">
-        <v>92818</v>
+        <v>92823</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1539,7 +1539,7 @@
         <v>128518177</v>
       </c>
       <c r="B9" t="n">
-        <v>92818</v>
+        <v>92823</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1633,32 +1633,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128518184</v>
+        <v>128518175</v>
       </c>
       <c r="B10" t="n">
-        <v>98646</v>
+        <v>92823</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>4366</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1668,10 +1668,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>555042</v>
+        <v>554991</v>
       </c>
       <c r="R10" t="n">
-        <v>6961890</v>
+        <v>6961943</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1730,32 +1730,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128518172</v>
+        <v>128518184</v>
       </c>
       <c r="B11" t="n">
-        <v>91017</v>
+        <v>98651</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>256703</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1765,10 +1765,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>555056</v>
+        <v>555042</v>
       </c>
       <c r="R11" t="n">
-        <v>6961814</v>
+        <v>6961890</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1827,10 +1827,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128518175</v>
+        <v>128518172</v>
       </c>
       <c r="B12" t="n">
-        <v>92818</v>
+        <v>91022</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1838,21 +1838,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4366</v>
+        <v>256703</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Tallfingersvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Ramaria eosanguinea</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>R.H.Petersen</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1862,10 +1862,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>554991</v>
+        <v>555056</v>
       </c>
       <c r="R12" t="n">
-        <v>6961943</v>
+        <v>6961814</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2024,7 +2024,7 @@
         <v>128518178</v>
       </c>
       <c r="B14" t="n">
-        <v>92818</v>
+        <v>92823</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2121,7 +2121,7 @@
         <v>128518176</v>
       </c>
       <c r="B15" t="n">
-        <v>92818</v>
+        <v>92823</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 34540-2025 artfynd.xlsx
+++ b/artfynd/A 34540-2025 artfynd.xlsx
@@ -1633,10 +1633,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128518175</v>
+        <v>128518172</v>
       </c>
       <c r="B10" t="n">
-        <v>92823</v>
+        <v>91022</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1644,21 +1644,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4366</v>
+        <v>256703</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Tallfingersvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Ramaria eosanguinea</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>R.H.Petersen</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1668,10 +1668,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>554991</v>
+        <v>555056</v>
       </c>
       <c r="R10" t="n">
-        <v>6961943</v>
+        <v>6961814</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1827,10 +1827,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128518172</v>
+        <v>128518175</v>
       </c>
       <c r="B12" t="n">
-        <v>91022</v>
+        <v>92823</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1838,21 +1838,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>256703</v>
+        <v>4366</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1862,10 +1862,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>555056</v>
+        <v>554991</v>
       </c>
       <c r="R12" t="n">
-        <v>6961814</v>
+        <v>6961943</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>

--- a/artfynd/A 34540-2025 artfynd.xlsx
+++ b/artfynd/A 34540-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AY16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,59 +675,56 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>96790360</v>
+        <v>121310766</v>
       </c>
       <c r="B2" t="n">
-        <v>90669</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93185</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2059</v>
+        <v>149</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Tallgråticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Boletopsis grisea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Peck) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Dragsjömon, Jmt</t>
+          <t>Dragsjömoarna, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>555068.4865219704</v>
+        <v>554988</v>
       </c>
       <c r="R2" t="n">
-        <v>6961789.681034689</v>
+        <v>6961961</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,22 +751,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2021-09-07</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2021-09-07</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-09</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -778,64 +765,51 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>olikåldrig sandtallskog, intill stig</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>96790357</v>
+        <v>96790359</v>
       </c>
       <c r="B3" t="n">
-        <v>90287</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4745</v>
+        <v>2059</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -854,10 +828,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>555038.5217428559</v>
+        <v>555037</v>
       </c>
       <c r="R3" t="n">
-        <v>6961854.192028894</v>
+        <v>6961836</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,21 +861,11 @@
           <t>2021-09-07</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2021-09-07</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -913,7 +877,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>35-årig sandtallskog i f.d. sandtag, nära äldre sandtallskog</t>
+          <t>olikåldrig sandtallskog, intill stig</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -935,37 +899,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>96790358</v>
+        <v>96790360</v>
       </c>
       <c r="B4" t="n">
-        <v>90665</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4366</v>
+        <v>2059</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -984,10 +943,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>555034.5867488543</v>
+        <v>555068</v>
       </c>
       <c r="R4" t="n">
-        <v>6961870.150237069</v>
+        <v>6961790</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1017,21 +976,11 @@
           <t>2021-09-07</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2021-09-07</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1043,7 +992,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>35-årig sandtallskog i f.d. sandtag, nära äldre sandtallskog</t>
+          <t>olikåldrig sandtallskog, intill stig</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1065,19 +1014,14 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>96790361</v>
+        <v>96790358</v>
       </c>
       <c r="B5" t="n">
-        <v>90665</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1114,10 +1058,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>555068.5861998007</v>
+        <v>555034</v>
       </c>
       <c r="R5" t="n">
-        <v>6961783.730761241</v>
+        <v>6961870</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1147,21 +1091,11 @@
           <t>2021-09-07</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2021-09-07</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1173,7 +1107,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>olikåldrig sandtallskog på stig</t>
+          <t>35-årig sandtallskog i f.d. sandtag, nära äldre sandtallskog</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1195,15 +1129,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>96790359</v>
+        <v>96790361</v>
       </c>
       <c r="B6" t="n">
-        <v>90669</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1211,21 +1140,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2059</v>
+        <v>4366</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1244,10 +1173,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>555036.9872087621</v>
+        <v>555068</v>
       </c>
       <c r="R6" t="n">
-        <v>6961836.310829996</v>
+        <v>6961784</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1277,21 +1206,11 @@
           <t>2021-09-07</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2021-09-07</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1303,7 +1222,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>olikåldrig sandtallskog, intill stig</t>
+          <t>olikåldrig sandtallskog på stig</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1325,61 +1244,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121310766</v>
+        <v>128518175</v>
       </c>
       <c r="B7" t="n">
-        <v>91992</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>149</v>
+        <v>4366</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tallgråticka</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Boletopsis grisea</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Peck) Bondartsev &amp; Singer</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Dragsjömoarna, Jmt</t>
+          <t>Strandåker, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>554988</v>
+        <v>554991</v>
       </c>
       <c r="R7" t="n">
-        <v>6961961</v>
+        <v>6961943</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1406,12 +1309,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2025-09-14</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-10-09</t>
+          <t>2025-09-14</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1420,33 +1323,32 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Erica Hästdahl</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Erica Hästdahl</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128518179</v>
+        <v>128518176</v>
       </c>
       <c r="B8" t="n">
-        <v>92823</v>
+        <v>93209</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1474,10 +1376,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>555066</v>
+        <v>555032</v>
       </c>
       <c r="R8" t="n">
-        <v>6961789</v>
+        <v>6961940</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1539,11 +1441,11 @@
         <v>128518177</v>
       </c>
       <c r="B9" t="n">
-        <v>92823</v>
+        <v>93209</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1633,32 +1535,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128518172</v>
+        <v>128518178</v>
       </c>
       <c r="B10" t="n">
-        <v>91022</v>
+        <v>93209</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>256703</v>
+        <v>4366</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1668,10 +1570,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>555056</v>
+        <v>555051</v>
       </c>
       <c r="R10" t="n">
-        <v>6961814</v>
+        <v>6961818</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1730,32 +1632,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128518184</v>
+        <v>128518179</v>
       </c>
       <c r="B11" t="n">
-        <v>98651</v>
+        <v>93209</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>4366</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1765,10 +1667,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>555042</v>
+        <v>555066</v>
       </c>
       <c r="R11" t="n">
-        <v>6961890</v>
+        <v>6961789</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1827,45 +1729,54 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128518175</v>
+        <v>96790357</v>
       </c>
       <c r="B12" t="n">
-        <v>92823</v>
+        <v>92841</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4366</v>
+        <v>4745</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Banker</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Strandåker, Jmt</t>
+          <t>Dragsjömon, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>554991</v>
+        <v>555039</v>
       </c>
       <c r="R12" t="n">
-        <v>6961943</v>
+        <v>6961854</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1892,12 +1803,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-09-14</t>
+          <t>2021-09-07</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-09-14</t>
+          <t>2021-09-07</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1908,26 +1819,35 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>35-årig sandtallskog i f.d. sandtag, nära äldre sandtallskog</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Erica Hästdahl</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Erica Hästdahl</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr"/>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
         <v>128518169</v>
       </c>
       <c r="B13" t="n">
-        <v>57883</v>
+        <v>58114</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2021,32 +1941,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128518178</v>
+        <v>128518184</v>
       </c>
       <c r="B14" t="n">
-        <v>92823</v>
+        <v>99118</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4366</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2056,10 +1976,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>555051</v>
+        <v>555042</v>
       </c>
       <c r="R14" t="n">
-        <v>6961818</v>
+        <v>6961890</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2118,32 +2038,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128518176</v>
+        <v>128518171</v>
       </c>
       <c r="B15" t="n">
-        <v>92823</v>
+        <v>91402</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4366</v>
+        <v>256703</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Tallfingersvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Ramaria eosanguinea</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>R.H.Petersen</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2153,10 +2073,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>555032</v>
+        <v>554986</v>
       </c>
       <c r="R15" t="n">
-        <v>6961940</v>
+        <v>6961929</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2212,6 +2132,103 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>128518172</v>
+      </c>
+      <c r="B16" t="n">
+        <v>91402</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>256703</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Tallfingersvamp</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Ramaria eosanguinea</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>R.H.Petersen</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Strandåker, Jmt</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>555056</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6961814</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-09-14</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 34540-2025 artfynd.xlsx
+++ b/artfynd/A 34540-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AZ16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -781,6 +786,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121310766</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -896,6 +906,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96790359</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1011,6 +1026,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96790360</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1126,6 +1146,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96790358</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1241,6 +1266,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96790361</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1338,6 +1368,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128518175</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1435,6 +1470,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128518176</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1532,6 +1572,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128518177</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1629,6 +1674,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128518178</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1726,6 +1776,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128518179</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1841,6 +1896,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96790357</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1938,6 +1998,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128518169</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2035,6 +2100,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128518184</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2132,6 +2202,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128518171</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2229,8 +2304,30 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128518172</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>